--- a/examples/transport_routing.xlsx
+++ b/examples/transport_routing.xlsx
@@ -7,10 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="supply" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="demand" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cost_matrix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="constraints" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="origins" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="destinations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="costs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,17 +421,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>supply</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>location</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>supply_units</t>
         </is>
       </c>
     </row>
@@ -442,13 +441,13 @@
           <t>WH_North</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" t="n">
         <v>350</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chicago IL</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -457,13 +456,13 @@
           <t>WH_South</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" t="n">
         <v>280</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Atlanta GA</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -472,13 +471,13 @@
           <t>WH_West</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" t="n">
         <v>420</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Los Angeles CA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -498,17 +497,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>store</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>location</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>demand_units</t>
         </is>
       </c>
     </row>
@@ -518,13 +517,13 @@
           <t>Store_A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Detroit, MI</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" t="n">
         <v>120</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Detroit MI</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -533,13 +532,13 @@
           <t>Store_B</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Nashville, TN</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" t="n">
         <v>150</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nashville TN</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -548,13 +547,13 @@
           <t>Store_C</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" t="n">
         <v>200</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Phoenix AZ</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -563,13 +562,13 @@
           <t>Store_D</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Denver, CO</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" t="n">
         <v>180</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Denver CO</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -578,13 +577,13 @@
           <t>Store_E</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Seattle, WA</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" t="n">
         <v>160</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Seattle WA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -604,7 +603,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>warehouse_store</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -697,69 +696,6 @@
       </c>
       <c r="F4" t="n">
         <v>1.8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>constraint</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>max_route_units</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>200</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max units on any single route (truck capacity)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>objective</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>minimize_cost</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Minimize total transport cost</t>
-        </is>
       </c>
     </row>
   </sheetData>
